--- a/catalogs/Saturn-сверка-трёх-источников.xlsx
+++ b/catalogs/Saturn-сверка-трёх-источников.xlsx
@@ -46,7 +46,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFD9CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F0ED"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -102,6 +107,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -490,7 +501,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="54" customWidth="1" min="10" max="10"/>
@@ -546,7 +557,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>СОСТАВ · каталог производителя (= подтверждённая)</t>
+          <t>СОСТАВ · каталог = подтверждённая</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -1021,7 +1032,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1071,7 +1082,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1121,7 +1132,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1171,7 +1182,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1221,7 +1232,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1271,7 +1282,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1321,7 +1332,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1549,7 +1560,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1797,7 +1808,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>SO3 980 г/л, MgO 31 г/л, N 27 г/л</t>
+          <t>SO3 980 г/л · MgO 31 г/л · N 27 г/л</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -2207,7 +2218,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>Магний 75 г/л, цинк 30 г/л, сера, азот 52 г/л, фосфор 14 г/л, КАЛИЙ 37 г/л</t>
+          <t>Магний 75 · Цинк 30 · Азот 52 · Сера 37 · Фосфор 14 · КАЛИЙ 37 г/л</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2327,7 +2338,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Марганец 56 г/л, цинк 28 г/л, азот 10 г/л, сера 120 г/л, фосфор 6 г/л, влагоудерживающая добавка</t>
+          <t>Марганец 56 · Цинк 28 · Азот 10 · Сера 120 · Фосфор 6 г/л, влагоудерживающая добавка</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2694,26 +2705,22 @@
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>0,5 л/га листовая подкормка (рапс — фазы розетка, стеблевание, бутонизация)</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>0,3–1,5 л/га</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>0,3-1,5 л/га листовая подкормка (рапс — фазы розетка, стеблевание, бутонизация)</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
+      <c r="I40" s="3" t="inlineStr"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
           <t>Сера (SO3) 550–600 г/л · азот (N) 110–130 г/л; рН 5–6. Сульфитная форма</t>
@@ -2798,26 +2805,22 @@
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>0,43–1,0 л/га листовая подкормка</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>0,3–1,5 л/га</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>0,3–1,5 л/га листовая подкормка</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
+      <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
           <t>Цинк (ZnO) 120–140 г/л · азот (N) 30–40 г/л · комплекс аминокислот 15–180 г/л; рН 5–6</t>
@@ -2913,7 +2916,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -2963,7 +2966,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -3013,7 +3016,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -3063,7 +3066,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -3113,7 +3116,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -3163,7 +3166,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -3213,7 +3216,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -3263,7 +3266,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
@@ -3313,7 +3316,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -3363,7 +3366,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
@@ -3413,7 +3416,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -3463,7 +3466,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
@@ -3513,7 +3516,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
@@ -3563,7 +3566,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
@@ -3613,7 +3616,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -3663,7 +3666,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>1,5–2</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
@@ -3713,7 +3716,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>1,4–5</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
@@ -3763,7 +3766,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>2–8</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
@@ -3813,7 +3816,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>1,5–4</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
@@ -3863,7 +3866,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,01–0,05</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
@@ -3913,7 +3916,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>1–1,5</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
@@ -3963,7 +3966,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,2–1</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
@@ -4013,7 +4016,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,3–0,5</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -4063,7 +4066,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
@@ -4113,7 +4116,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,7–1</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -4163,7 +4166,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,75–1</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
@@ -4213,7 +4216,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>1,3–1,6</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -4263,7 +4266,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,8–1</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
@@ -4313,7 +4316,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,5–1</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -4363,7 +4366,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,006–0,025</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
@@ -4413,7 +4416,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,025–0,035</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
@@ -4463,7 +4466,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,4–0,9</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
@@ -4513,7 +4516,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,5–1,5</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
@@ -4563,7 +4566,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>1–1,2</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
@@ -4613,7 +4616,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
@@ -4663,7 +4666,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,7–1,8</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
@@ -4713,7 +4716,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,4–0,5</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
@@ -4763,7 +4766,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,5–1</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
@@ -4813,7 +4816,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,5–9</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
@@ -4863,7 +4866,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,3–12</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
@@ -4913,7 +4916,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,1–0,3</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
@@ -4963,7 +4966,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,1–0,5</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
@@ -5013,7 +5016,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,1–0,25</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
@@ -5063,7 +5066,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,5–1</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
@@ -5113,7 +5116,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,4–0,75</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
@@ -5163,7 +5166,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,2–0,6</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
@@ -5213,7 +5216,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,75–1</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
@@ -5513,7 +5516,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,01–0,1</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
@@ -5563,7 +5566,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,8–1,5</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
@@ -5613,7 +5616,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,1–0,3</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
@@ -5663,7 +5666,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>не задана в прайсе</t>
+          <t>0,5–1</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
@@ -5685,54 +5688,54 @@
       <c r="L99" s="3" t="inlineStr"/>
     </row>
     <row r="100" ht="70" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>Волски Аминатор</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr"/>
+      <c r="B100" s="6" t="inlineStr"/>
       <c r="C100" s="4" t="inlineStr">
         <is>
+          <t>нет в прайсе</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>от 900 р.</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>от 900 р.</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>нет в прайсе</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr"/>
+      <c r="J100" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>не задана в прайсе</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr"/>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>совпадает</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="inlineStr"/>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>совпадает</t>
+        </is>
+      </c>
+      <c r="L100" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L100"/>
@@ -5746,7 +5749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5754,182 +5757,170 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>ИСТОЧНИКИ</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr"/>
+      <c r="B1" s="8" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>1. Каталог производителя</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>Выгрузка из PDF-каталогов «Фертика», «Волски Биохим» и ГК «Генезис». Цен там нет — только состав, нормы, культуры.</t>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Выгрузка из PDF-каталогов «Фертика», «Волски Биохим», ГК «Генезис». Цен там нет.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>2. Прайс «Сатурна»</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Прайс-лист сезона 2026, действует с 12.01.2026. Цены — оттуда. Нормы прочитаны построчно с оригинала при 300 dpi.</t>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Прайс-лист сезона 2026 (с 12.01.2026). Все 5 страниц прочитаны построчно с оригинала при 300 dpi.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>3. Подтверждённая таблица</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Файл с правками заказчика от 25.09.2026 — действующий первоисточник.</t>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Правки заказчика от 25.09.2026 — действующий первоисточник.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr"/>
+      <c r="A5" s="9" t="inlineStr"/>
+      <c r="B5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>ПОДСВЕТКА</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Розовым — ячейки, где источники расходятся. В колонках «Δ» стоит ✗.</t>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Розовым — расхождения. Серым — позиции, которых в прайсе «Сатурна» нет вообще (OYYO, Relict Макро, Аминатор, Микроэл пивоваренный).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr"/>
+      <c r="A7" s="9" t="inlineStr"/>
+      <c r="B7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОЖДЕНИЙ</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr"/>
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>По цене</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>21 позиций (прайс ↔ подтверждённая)</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Расхождений по цене</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>21 позиций</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>По норме расхода</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>33 позиций</t>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Расхождений по норме</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>31 позиций</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>По составу</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Расхождений по составу</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>3 позиции</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr"/>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Нет в прайсе вообще</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>1 позиций — сверять не с чем</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr"/>
+      <c r="B13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>КАК ЭТО ПОНИМАТЬ</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Цены</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Расхождения — это правки заказчика от 25.09, а не ошибки. Действует подтверждённая таблица.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Расхождения — правки заказчика от 25.09, а не ошибки. Действует подтверждённая таблица.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Нормы</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Главная проблема. Заказчик правил только отдельные строки, поэтому у большинства позиций в подтверждённой таблице остались нормы из каталогов производителей. Прайс «Сатурна» даёт другие. Нужно решение, какие считать верными — сейчас сайт и прайс разойдутся.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Главная проблема: заказчик правил выборочно, поэтому у большинства позиций остались нормы производителей, а прайс даёт свои. Нужно решение, какие верны.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Состав</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Колонки 1 и 3 совпадают: подтверждённая таблица построена на нашей выгрузке из каталогов, составы заказчик не правил. Поэтому здесь сравнение идёт с ПРАЙСОМ. Прайс даёт сокращённые формулировки — сравнивались только по существу, не по тексту. Найдено 3 содержательных расхождения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr"/>
-      <c r="B17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>ЧЕГО В ТАБЛИЦЕ НЕТ</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Состав по прайсу заполнен не везде</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Формулировки в прайсе короче каталожных, и дословно переносить их смысла нет. Колонка заполнена только там, где прайс сообщает то, чего нет в каталоге.</t>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Колонки 1 и 3 совпадают по построению — подтверждённая таблица выросла из нашей выгрузки. Поэтому сравнение идёт с прайсом, и только по существу: формулировки в прайсе короче.</t>
         </is>
       </c>
     </row>
